--- a/tame_output/ON/bt/strategyON_20240408.xlsx
+++ b/tame_output/ON/bt/strategyON_20240408.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-516.9%</t>
+          <t>-517.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-209.9%</t>
+          <t>-210.0%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-213.5%</t>
+          <t>-213.6%</t>
         </is>
       </c>
     </row>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094122</v>
+        <v>3.374439043094121</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.4246333549696</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923093</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297755</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317622</v>
+        <v>3.447750501317621</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737176</v>
+        <v>3.503515506737175</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341319</v>
+        <v>3.503170282341318</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282103</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425331</v>
+        <v>3.72857435442533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.747699084702414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631350390623</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487776</v>
+        <v>3.789307536487775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83324917230973</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858732</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096478</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-3.55345532560211</v>
+        <v>-3.556505317687175</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.663616403292014</v>
+        <v>1.662396406457988</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1045797756724739</v>
+        <v>0.1041294198763657</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.14810282325009</v>
+        <v>3.147832609772425</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240408.xlsx
+++ b/tame_output/ON/bt/strategyON_20240408.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.1%</t>
+          <t>116.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.9%</t>
+          <t>135.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-74.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>497.7%</t>
+          <t>497.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-517.2%</t>
+          <t>-540.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-210.0%</t>
+          <t>-219.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-25.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-19.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-213.6%</t>
+          <t>-220.1%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-131.2%</t>
+          <t>-135.2%</t>
         </is>
       </c>
     </row>
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-3.556505317687175</v>
+        <v>-3.792860745423056</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.662396406457988</v>
+        <v>1.567854235363636</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1041294198763657</v>
+        <v>0.03881048378652541</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.147832609772425</v>
+        <v>3.108641248118521</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240408.xlsx
+++ b/tame_output/ON/bt/strategyON_20240408.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,75 +801,75 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-32.7%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.7%</t>
+          <t>116.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.8%</t>
+          <t>135.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-135.2%</t>
+          <t>-167.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1927"/>
+  <dimension ref="A1:G1928"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199291</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317621</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737175</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341318</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776682</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.474088693347393</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
@@ -45882,6 +45882,29 @@
       </c>
       <c r="G1927" t="n">
         <v>3.108641248118521</v>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" s="2" t="n">
+        <v>45390</v>
+      </c>
+      <c r="B1928" t="n">
+        <v>3.47434393230585</v>
+      </c>
+      <c r="C1928" t="n">
+        <v>2.789237012981384</v>
+      </c>
+      <c r="D1928" t="n">
+        <v>-3.792860745423056</v>
+      </c>
+      <c r="E1928" t="n">
+        <v>1.567854235363636</v>
+      </c>
+      <c r="F1928" t="n">
+        <v>0.03881048378652541</v>
+      </c>
+      <c r="G1928" t="n">
+        <v>2.782300809967752</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240408.xlsx
+++ b/tame_output/ON/bt/strategyON_20240408.xlsx
@@ -45892,7 +45892,7 @@
         <v>3.47434393230585</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.789237012981384</v>
+        <v>2.789237012981383</v>
       </c>
       <c r="D1928" t="n">
         <v>-3.792860745423056</v>
@@ -45904,7 +45904,7 @@
         <v>0.03881048378652541</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.782300809967752</v>
+        <v>2.782300809967751</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240408.xlsx
+++ b/tame_output/ON/bt/strategyON_20240408.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>53.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,75 +801,75 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-3.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.6%</t>
+          <t>117.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-665.0%</t>
+          <t>-664.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-54.5%</t>
+          <t>-54.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.4%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>497.2%</t>
+          <t>502.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-540.9%</t>
+          <t>-515.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-260.6%</t>
+          <t>-260.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-219.4%</t>
+          <t>-209.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.2%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-220.1%</t>
+          <t>-213.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-167.8%</t>
+          <t>-138.6%</t>
         </is>
       </c>
     </row>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094121</v>
+        <v>3.374439043094122</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.065245534582596</v>
+        <v>-8.056695079743092</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1130714592534008</v>
+        <v>-0.109651277317599</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.629197193151051</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.070058573047932</v>
+        <v>-8.061508118208428</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1112176987103273</v>
+        <v>-0.1077975167745255</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.630743827853836</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.503407681158167</v>
+        <v>-8.494857226318663</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2885836464888243</v>
+        <v>-0.2851634645530225</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.630743827853836</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.886409069900798</v>
+        <v>-8.877858615061294</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4418863033074611</v>
+        <v>-0.4384661213716594</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.630743827853836</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.261394396072076</v>
+        <v>-9.252843941232571</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5893089178045416</v>
+        <v>-0.5858887358687399</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.005729154025114</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.620924718576077</v>
+        <v>-9.612374263736573</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.727770743508092</v>
+        <v>-0.7243505615722903</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.005729154025114</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.94732474724109</v>
+        <v>-9.938774292401586</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.85041473501692</v>
+        <v>-0.8469945530811183</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.332129182690127</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.940848600447531</v>
+        <v>-9.932298145608026</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.844782525677727</v>
+        <v>-0.8413623437419253</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.325653035896567</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.93715767549112</v>
+        <v>-9.928607220651616</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8433061556951631</v>
+        <v>-0.8398859737593614</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.325653035896567</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.14141585082098</v>
+        <v>-10.13286539598148</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.919496228708466</v>
+        <v>-0.9160760467726643</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.453291980510556</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.30205487730935</v>
+        <v>-10.29350442246984</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.979269284819376</v>
+        <v>-0.9758491028835743</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.568025453512952</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.2285850456419</v>
+        <v>-10.2200345908024</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.934509650658975</v>
+        <v>-0.9310894687231732</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.494555621845504</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.40370946302844</v>
+        <v>-10.39515900818894</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9900041968660762</v>
+        <v>-0.9865840149302745</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.669680039232047</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.63816155704293</v>
+        <v>-10.62961110220343</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.091004199373467</v>
+        <v>-1.087584017437666</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.669680039232047</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.92596540158017</v>
+        <v>-10.91741494674067</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.21279792796234</v>
+        <v>-1.209377746026538</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.957483883769286</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.155789848744</v>
+        <v>-11.14723939390449</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.303611916989313</v>
+        <v>-1.300191735053511</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.120131420839446</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.38781876848026</v>
+        <v>-11.37926831364075</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.393729756254703</v>
+        <v>-1.390309574318902</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.182144118027869</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.33580325451145</v>
+        <v>-11.32725279967194</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.368933214980777</v>
+        <v>-1.365513033044976</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.182144118027869</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.47747509623557</v>
+        <v>-11.46892464139606</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.427077178569167</v>
+        <v>-1.423656996633365</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.182144118027869</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.57638183669484</v>
+        <v>-11.56783138185534</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.451586464588005</v>
+        <v>-1.448166282652203</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.281050858487145</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.37722972945774</v>
+        <v>-11.36867927461824</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.384976755339848</v>
+        <v>-1.381556573404046</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.115728332537332</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.15138457673833</v>
+        <v>-11.14283412189883</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.285059621215875</v>
+        <v>-1.281639439280073</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.073801656950168</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.86510976441564</v>
+        <v>-10.85655930957613</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.169410551730738</v>
+        <v>-1.165990369794936</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.073801656950168</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.91800505245992</v>
+        <v>-10.90945459762042</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.187934892786345</v>
+        <v>-1.184514710850543</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.068846310861722</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.63409632153117</v>
+        <v>-10.62554586669167</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.068637696176209</v>
+        <v>-1.065217514240407</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.068846310861722</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.38710907133822</v>
+        <v>-10.37855861649872</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9795800584928935</v>
+        <v>-0.9761598765570918</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.82185906066877</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.12327220413415</v>
+        <v>-10.11472174929465</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.883928792924173</v>
+        <v>-0.8805086109883713</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.82185906066877</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.856030403265754</v>
+        <v>-9.847479948426249</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7788666330761878</v>
+        <v>-0.775446451140386</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.82185906066877</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.580221239865269</v>
+        <v>-9.571670785025765</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6688432826894544</v>
+        <v>-0.6654231007536526</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.732839752390036</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.556267698889311</v>
+        <v>-9.547717244049807</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6585933601535778</v>
+        <v>-0.6551731782177761</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.708886211414079</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.292207760566514</v>
+        <v>-9.28365730572701</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5662297009862112</v>
+        <v>-0.5628095190504094</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.444826273091283</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.585128137061677</v>
+        <v>-8.576577682222172</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2861848852445772</v>
+        <v>-0.2827647033087755</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.444826273091283</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.335487107075725</v>
+        <v>-8.32693665223622</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.185984849362355</v>
+        <v>-0.1825646674265533</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.195185243105331</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.080945207734649</v>
+        <v>-8.072394752895145</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.08480126840516755</v>
+        <v>-0.08138108646936582</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.940643343764255</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.84746398550505</v>
+        <v>-7.838913530665546</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.01651564932452398</v>
+        <v>0.01993583126032572</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.707162121534657</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.667755455361178</v>
+        <v>-7.659205000521673</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.08550685106911393</v>
+        <v>0.08892703300491567</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.649990617371961</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.535479981730291</v>
+        <v>-7.526929526890787</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.1337845272684954</v>
+        <v>0.1372047092042972</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.517715143741074</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.344880307057139</v>
+        <v>-7.336329852217634</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2128394578253934</v>
+        <v>0.2162596397611951</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.327115469067921</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.095880508373558</v>
+        <v>-7.087330053534053</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3253457185224846</v>
+        <v>0.3287659004582864</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.327115469067921</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.201470498146662</v>
+        <v>-7.192920043307158</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.155133793014024</v>
+        <v>0.1585539749498257</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.432705458841026</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.220205400265259</v>
+        <v>-7.211654945425755</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1961841740436716</v>
+        <v>0.1996043559794733</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.432705458841026</v>
@@ -45481,10 +45481,10 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.943467225594446</v>
+        <v>-6.934916770754942</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3102584558979915</v>
+        <v>0.3136786378337932</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.2508887977311</v>
@@ -45504,10 +45504,10 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.816574819159376</v>
+        <v>-6.808024364319872</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3523014322185412</v>
+        <v>0.3557216141543429</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.12399639129603</v>
@@ -45527,10 +45527,10 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.62898731124945</v>
+        <v>-6.620436856409945</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4203758232874186</v>
+        <v>0.4237960052232204</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.12399639129603</v>
@@ -45550,10 +45550,10 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.386838917795592</v>
+        <v>-6.378288462956087</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.531697535050105</v>
+        <v>0.5351177169859067</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.12399639129603</v>
@@ -45573,10 +45573,10 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.323609546027243</v>
+        <v>-6.315059091187739</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5515214042166394</v>
+        <v>0.5549415861524412</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.12399639129603</v>
@@ -45596,10 +45596,10 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.137121853650237</v>
+        <v>-6.128571398810733</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6236145751780189</v>
+        <v>0.6270347571138206</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.9375086989190236</v>
@@ -45619,10 +45619,10 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.115972654746794</v>
+        <v>-6.10742219990729</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6397752329767217</v>
+        <v>0.6431954149125234</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.9163595000155802</v>
@@ -45642,10 +45642,10 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.87220721276335</v>
+        <v>-5.863656757923845</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7330621181171502</v>
+        <v>0.7364823000529519</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.9163595000155802</v>
@@ -45665,10 +45665,10 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.608179145570089</v>
+        <v>-5.599628690730585</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.8407976589144703</v>
+        <v>0.8442178408502721</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.7144941011996266</v>
@@ -45688,10 +45688,10 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.358328751621015</v>
+        <v>-5.34977829678151</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.9334798914778024</v>
+        <v>0.9369000734136042</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.7144941011996266</v>
@@ -45711,10 +45711,10 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.054761262617036</v>
+        <v>-5.046210807777531</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.058506010600043</v>
+        <v>1.061926192535844</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.7144941011996266</v>
@@ -45734,10 +45734,10 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.981281353765022</v>
+        <v>-4.972730898925517</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.101225480195402</v>
+        <v>1.104645662131204</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.6410141923476123</v>
@@ -45757,10 +45757,10 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.756248354096199</v>
+        <v>-4.747697899256694</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.190259157679228</v>
+        <v>1.19367933961503</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.4159811926787894</v>
@@ -45780,10 +45780,10 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.541613976459792</v>
+        <v>-4.533063521620288</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.280807709788108</v>
+        <v>1.28422789172391</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.2013468150423826</v>
@@ -45803,10 +45803,10 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.27501361948544</v>
+        <v>-4.266463164645936</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.368642111361644</v>
+        <v>1.372062293297446</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.2013468150423826</v>
@@ -45826,10 +45826,10 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.03458312268058</v>
+        <v>-4.026032667841076</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.466557386708466</v>
+        <v>1.469977568644268</v>
       </c>
       <c r="F1925" t="n">
         <v>0.03908368176247767</v>
@@ -45849,10 +45849,10 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-3.791792315031135</v>
+        <v>-3.78324186019163</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.567603023603064</v>
+        <v>1.571023205538866</v>
       </c>
       <c r="F1926" t="n">
         <v>0.03908368176247767</v>
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.82232342234997</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-3.792860745423056</v>
+        <v>-3.543636768584541</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.567854235363636</v>
+        <v>1.667543826099042</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.03881048378652541</v>
+        <v>0.1061316294309722</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.108641248118521</v>
+        <v>3.149033935505189</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.47434393230585</v>
+        <v>3.815080727204132</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.789237012981383</v>
+        <v>3.080957043693927</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.792860745423056</v>
+        <v>-3.543636768584541</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.567854235363636</v>
+        <v>1.667543826099042</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.03881048378652541</v>
+        <v>0.1061316294309722</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.782300809967751</v>
+        <v>3.074020840680295</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240408.xlsx
+++ b/tame_output/ON/bt/strategyON_20240408.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>22.0%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-77.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.1%</t>
+          <t>114.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.7%</t>
+          <t>135.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1002,22 +1002,22 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-72.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>502.5%</t>
+          <t>498.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-515.9%</t>
+          <t>-522.0%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-53.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-209.5%</t>
+          <t>-212.3%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-138.6%</t>
+          <t>-131.6%</t>
         </is>
       </c>
     </row>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.576577682222172</v>
+        <v>-8.883114514941735</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2827647033087755</v>
+        <v>-0.4053794363966001</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.444826273091283</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.32693665223622</v>
+        <v>-8.633473484955783</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.1825646674265533</v>
+        <v>-0.305179400514378</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.195185243105331</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.072394752895145</v>
+        <v>-8.378931585614707</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.08138108646936582</v>
+        <v>-0.2039958195571909</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.940643343764255</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.838913530665546</v>
+        <v>-8.145450363385109</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.01993583126032572</v>
+        <v>-0.1026789018274994</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.707162121534657</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.659205000521673</v>
+        <v>-7.965741833241236</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.08892703300491567</v>
+        <v>-0.03368770008290944</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.649990617371961</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.526929526890787</v>
+        <v>-7.83346635961035</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.1372047092042972</v>
+        <v>0.01458997611647206</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.517715143741074</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.336329852217634</v>
+        <v>-7.642866684937197</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2162596397611951</v>
+        <v>0.09364490667337</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.327115469067921</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.087330053534053</v>
+        <v>-7.393866886253616</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3287659004582864</v>
+        <v>0.2061511673704612</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.327115469067921</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.192920043307158</v>
+        <v>-7.499456876026721</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.1585539749498257</v>
+        <v>0.03593924186200059</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.432705458841026</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.211654945425755</v>
+        <v>-7.518191778145318</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1996043559794733</v>
+        <v>0.07698962289164824</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.432705458841026</v>
@@ -45481,10 +45481,10 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.934916770754942</v>
+        <v>-7.241453603474506</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3136786378337932</v>
+        <v>0.1910639047459677</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.2508887977311</v>
@@ -45504,10 +45504,10 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.808024364319872</v>
+        <v>-7.114561197039436</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3557216141543429</v>
+        <v>0.2331068810665173</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.12399639129603</v>
@@ -45527,10 +45527,10 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.620436856409945</v>
+        <v>-6.926973689129509</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4237960052232204</v>
+        <v>0.3011812721353948</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.12399639129603</v>
@@ -45550,10 +45550,10 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.378288462956087</v>
+        <v>-6.684825295675651</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5351177169859067</v>
+        <v>0.4125029838980812</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.12399639129603</v>
@@ -45573,10 +45573,10 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.315059091187739</v>
+        <v>-6.621595923907303</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5549415861524412</v>
+        <v>0.4323268530646156</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.12399639129603</v>
@@ -45596,10 +45596,10 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.128571398810733</v>
+        <v>-6.435108231530297</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6270347571138206</v>
+        <v>0.5044200240259951</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.9375086989190236</v>
@@ -45619,10 +45619,10 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.10742219990729</v>
+        <v>-6.413959032626853</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6431954149125234</v>
+        <v>0.5205806818246979</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.9163595000155802</v>
@@ -45642,10 +45642,10 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.863656757923845</v>
+        <v>-6.170193590643409</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7364823000529519</v>
+        <v>0.6138675669651263</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.9163595000155802</v>
@@ -45665,10 +45665,10 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.599628690730585</v>
+        <v>-5.906165523450149</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.8442178408502721</v>
+        <v>0.7216031077624465</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.7144941011996266</v>
@@ -45688,10 +45688,10 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.34977829678151</v>
+        <v>-5.656315129501074</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.9369000734136042</v>
+        <v>0.8142853403257786</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.7144941011996266</v>
@@ -45711,10 +45711,10 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.046210807777531</v>
+        <v>-5.352747640497095</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.061926192535844</v>
+        <v>0.9393114594480187</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.7144941011996266</v>
@@ -45734,10 +45734,10 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.972730898925517</v>
+        <v>-5.279267731645081</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.104645662131204</v>
+        <v>0.9820309290433782</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.6410141923476123</v>
@@ -45757,10 +45757,10 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.747697899256694</v>
+        <v>-5.054234731976258</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.19367933961503</v>
+        <v>1.071064606527204</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.4159811926787894</v>
@@ -45780,10 +45780,10 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.533063521620288</v>
+        <v>-4.839600354339852</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.28422789172391</v>
+        <v>1.161613158636084</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.2013468150423826</v>
@@ -45803,10 +45803,10 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.266463164645936</v>
+        <v>-4.5729999973655</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.372062293297446</v>
+        <v>1.24944756020962</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.2013468150423826</v>
@@ -45826,10 +45826,10 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.026032667841076</v>
+        <v>-4.332569500560639</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.469977568644268</v>
+        <v>1.347362835556442</v>
       </c>
       <c r="F1925" t="n">
         <v>0.03908368176247767</v>
@@ -45849,10 +45849,10 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-3.78324186019163</v>
+        <v>-4.089778692911194</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.571023205538866</v>
+        <v>1.44840847245104</v>
       </c>
       <c r="F1926" t="n">
         <v>0.03908368176247767</v>
@@ -45872,10 +45872,10 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-3.543636768584541</v>
+        <v>-3.850173601304105</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.667543826099042</v>
+        <v>1.544929093011216</v>
       </c>
       <c r="F1927" t="n">
         <v>0.1061316294309722</v>
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.815080727204132</v>
+        <v>3.500893714587327</v>
       </c>
       <c r="C1928" t="n">
         <v>3.080957043693927</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.543636768584541</v>
+        <v>-3.604563963448825</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.667543826099042</v>
+        <v>1.63877503400065</v>
       </c>
       <c r="F1928" t="n">
         <v>0.1061316294309722</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.074020840680295</v>
+        <v>3.144636021352511</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240408.xlsx
+++ b/tame_output/ON/bt/strategyON_20240408.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>22.9%</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.0%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.8%</t>
+          <t>118.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.8%</t>
+          <t>137.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-664.1%</t>
+          <t>-694.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-54.4%</t>
+          <t>-55.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.3%</t>
+          <t>-73.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>498.2%</t>
+          <t>498.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-522.0%</t>
+          <t>-521.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-260.3%</t>
+          <t>-272.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.5%</t>
+          <t>-43.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-53.3%</t>
+          <t>-52.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-212.3%</t>
+          <t>-212.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-36.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.7%</t>
+          <t>-154.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-213.4%</t>
+          <t>-220.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-30.7%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-131.6%</t>
+          <t>-135.5%</t>
         </is>
       </c>
     </row>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199291</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.056695079743092</v>
+        <v>-8.065245534582596</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.109651277317599</v>
+        <v>-0.1130714592534008</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.629197193151051</v>
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.061508118208428</v>
+        <v>-8.361906876392794</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1077975167745255</v>
+        <v>-0.2279570200482719</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.630743827853836</v>
+        <v>-1.697940328884929</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.138715858110292</v>
+        <v>2.098397957491636</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.494857226318663</v>
+        <v>-8.795255984503029</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2851634645530225</v>
+        <v>-0.4053229678267694</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.630743827853836</v>
+        <v>-1.697940328884929</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.134689553575888</v>
+        <v>2.094371652957232</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.877858615061294</v>
+        <v>-9.17825737324566</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4384661213716594</v>
+        <v>-0.5586256246454058</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.630743827853836</v>
+        <v>-1.697940328884929</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.134587452254304</v>
+        <v>2.094269551635648</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.252843941232571</v>
+        <v>-9.553242699416938</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5858887358687399</v>
+        <v>-0.7060482391424867</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.005729154025114</v>
+        <v>-2.072925655056207</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.912167772522968</v>
+        <v>1.871849871904312</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.612374263736573</v>
+        <v>-9.912773021920939</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7243505615722903</v>
+        <v>-0.8445100648460371</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.005729154025114</v>
+        <v>-2.072925655056207</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.917518075821018</v>
+        <v>1.877200175202362</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.938774292401586</v>
+        <v>-10.23917305058595</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.8469945530811183</v>
+        <v>-0.9671540563548651</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.332129182690127</v>
+        <v>-2.39932568372122</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.729594078579188</v>
+        <v>1.689276177960532</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.932298145608026</v>
+        <v>-10.23269690379239</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8413623437419253</v>
+        <v>-0.9615218470156717</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.325653035896567</v>
+        <v>-2.39284953692766</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.736521517277092</v>
+        <v>1.696203616658437</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.928607220651616</v>
+        <v>-10.22900597883598</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8398859737593614</v>
+        <v>-0.9600454770331077</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.325653035896567</v>
+        <v>-2.39284953692766</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.736521517277092</v>
+        <v>1.696203616658437</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.13286539598148</v>
+        <v>-10.43326415416585</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9160760467726643</v>
+        <v>-1.036235550046411</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.453291980510556</v>
+        <v>-2.520488481541649</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.665451347627342</v>
+        <v>1.625133447008686</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.29350442246984</v>
+        <v>-10.59390318065421</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9758491028835743</v>
+        <v>-1.096008606157321</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.568025453512952</v>
+        <v>-2.635221954544045</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.60109381831034</v>
+        <v>1.560775917691684</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.2200345908024</v>
+        <v>-10.52043334898676</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9310894687231732</v>
+        <v>-1.05124897199692</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.494555621845504</v>
+        <v>-2.561752122876596</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.66054741880423</v>
+        <v>1.620229518185575</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.39515900818894</v>
+        <v>-10.69555776637331</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9865840149302745</v>
+        <v>-1.106743518204021</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.669680039232047</v>
+        <v>-2.73687654026314</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.570027989119821</v>
+        <v>1.529710088501165</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.62961110220343</v>
+        <v>-10.93000986038779</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.087584017437666</v>
+        <v>-1.207743520711413</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.669680039232047</v>
+        <v>-2.73687654026314</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.562808824218225</v>
+        <v>1.522490923599569</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.91741494674067</v>
+        <v>-11.21781370492503</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.209377746026538</v>
+        <v>-1.329537249300284</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.957483883769286</v>
+        <v>-3.024680384800378</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.383454326721906</v>
+        <v>1.34313642610325</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.14723939390449</v>
+        <v>-11.44763815208886</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.300191735053511</v>
+        <v>-1.420351238327258</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.120131420839446</v>
+        <v>-3.187327921870539</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.286981594318366</v>
+        <v>1.24666369369971</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.37926831364075</v>
+        <v>-11.67966707182512</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.390309574318902</v>
+        <v>-1.510469077592648</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.182144118027869</v>
+        <v>-3.249340619058962</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.252467704634427</v>
+        <v>1.212149804015771</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.32725279967194</v>
+        <v>-11.62765155785631</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.365513033044976</v>
+        <v>-1.485672536318722</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.182144118027869</v>
+        <v>-3.249340619058962</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.256458040320827</v>
+        <v>1.216140139702172</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.46892464139606</v>
+        <v>-11.76932339958043</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.423656996633365</v>
+        <v>-1.543816499907112</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.182144118027869</v>
+        <v>-3.249340619058962</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.254982813422086</v>
+        <v>1.21466491280343</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.56783138185534</v>
+        <v>-11.8682301400397</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.448166282652203</v>
+        <v>-1.568325785925949</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.281050858487145</v>
+        <v>-3.348247359518238</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.210692179311393</v>
+        <v>1.170374278692737</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.36867927461824</v>
+        <v>-11.6690780328026</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.381556573404046</v>
+        <v>-1.501716076677793</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.115728332537332</v>
+        <v>-3.182924833568424</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.296834561234598</v>
+        <v>1.256516660615942</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.14283412189883</v>
+        <v>-11.44323288008319</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.281639439280073</v>
+        <v>-1.401798942553821</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.073801656950168</v>
+        <v>-3.140998157981261</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.331569639623104</v>
+        <v>1.291251739004449</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.85655930957613</v>
+        <v>-11.1569580677605</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.165990369794936</v>
+        <v>-1.286149873068684</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.073801656950168</v>
+        <v>-3.140998157981261</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.332708784179163</v>
+        <v>1.292390883560508</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.90945459762042</v>
+        <v>-11.20985335580479</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.184514710850543</v>
+        <v>-1.30467421412429</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.068846310861722</v>
+        <v>-3.136042811892815</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.338315765994339</v>
+        <v>1.297997865375683</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.62554586669167</v>
+        <v>-10.92594462487604</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.065217514240407</v>
+        <v>-1.185377017514154</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.068846310861722</v>
+        <v>-3.136042811892815</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.344049470232975</v>
+        <v>1.303731569614319</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857435442533</v>
+        <v>3.728574354425331</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.37855861649872</v>
+        <v>-10.67895737468309</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9761598765570918</v>
+        <v>-1.096319379830839</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.82185906066877</v>
+        <v>-2.889055561699863</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.482504557954881</v>
+        <v>1.442186657336225</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702414</v>
+        <v>3.747699084702415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.11472174929465</v>
+        <v>-10.41512050747902</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8805086109883713</v>
+        <v>-1.000668114262119</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.82185906066877</v>
+        <v>-2.889055561699863</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.472621076641974</v>
+        <v>1.432303176023318</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.76631350390623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.847479948426249</v>
+        <v>-10.14787870661062</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.775446451140386</v>
+        <v>-0.8956059544141328</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.82185906066877</v>
+        <v>-2.889055561699863</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.4707865161426</v>
+        <v>1.430468615523944</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.571670785025765</v>
+        <v>-9.872069543210133</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6654231007536526</v>
+        <v>-0.7855826040273999</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.732839752390036</v>
+        <v>-2.800036253421129</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.523897786136379</v>
+        <v>1.483579885517723</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.547717244049807</v>
+        <v>-9.848116002234175</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6551731782177761</v>
+        <v>-0.7753326814915233</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.708886211414079</v>
+        <v>-2.776082712445171</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.538938416867447</v>
+        <v>1.498620516248791</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487775</v>
+        <v>3.789307536487776</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.28365730572701</v>
+        <v>-9.584056063911378</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5628095190504094</v>
+        <v>-0.6829690223241567</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.444826273091283</v>
+        <v>-2.512022774122376</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.684114063699373</v>
+        <v>1.643796163080717</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.883114514941735</v>
+        <v>-8.876976440406541</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4053794363966001</v>
+        <v>-0.4029242065825227</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.444826273091283</v>
+        <v>-2.512022774122376</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.681327030039072</v>
+        <v>1.641009129420416</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.633473484955783</v>
+        <v>-8.627335410420589</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.305179400514378</v>
+        <v>-0.3027241707003006</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.195185243105331</v>
+        <v>-2.262381744136424</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.831455271918484</v>
+        <v>1.791137371299828</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.378931585614707</v>
+        <v>-8.372793511079513</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2039958195571909</v>
+        <v>-0.2015405897431131</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.940643343764255</v>
+        <v>-2.007839844795348</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.983547232743887</v>
+        <v>1.943229332125231</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.145450363385109</v>
+        <v>-8.139312288849915</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1026789018274994</v>
+        <v>-0.1002236720134215</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.707162121534657</v>
+        <v>-1.774358622565749</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.131560394919498</v>
+        <v>2.091242494300842</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.965741833241236</v>
+        <v>-7.959603758706042</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.03368770008290944</v>
+        <v>-0.03123247026883202</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.649990617371961</v>
+        <v>-1.717187118403053</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.162971087104157</v>
+        <v>2.1226531864855</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.83346635961035</v>
+        <v>-7.827328285075156</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.01458997611647206</v>
+        <v>0.01704520593054992</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.517715143741074</v>
+        <v>-1.584911644772167</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.237703858029715</v>
+        <v>2.19738595741106</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.642866684937197</v>
+        <v>-7.636728610402003</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.09364490667337</v>
+        <v>0.09610013648744742</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.327115469067921</v>
+        <v>-1.394311970099014</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.354878723521244</v>
+        <v>2.314560822902588</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.393866886253616</v>
+        <v>-7.387728811718422</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2061511673704612</v>
+        <v>0.2086063971845387</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.327115469067921</v>
+        <v>-1.394311970099014</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.367785064744903</v>
+        <v>2.327467164126247</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.499456876026721</v>
+        <v>-7.493318801491527</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.03593924186200059</v>
+        <v>0.03839447167607801</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.432705458841026</v>
+        <v>-1.499901959872118</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.176455141281822</v>
+        <v>2.136137240663166</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.518191778145318</v>
+        <v>-7.512053703610124</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.07698962289164824</v>
+        <v>0.07944485270572565</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.432705458841026</v>
+        <v>-1.499901959872118</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.224999483158908</v>
+        <v>2.184681582540252</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.241453603474506</v>
+        <v>-7.235315528939312</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1910639047459677</v>
+        <v>0.1935191345600451</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.2508887977311</v>
+        <v>-1.318085298762192</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.337468491810858</v>
+        <v>2.297150591192202</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.114561197039436</v>
+        <v>-7.108423122504242</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2331068810665173</v>
+        <v>0.2355621108805952</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.12399639129603</v>
+        <v>-1.191192892327122</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.404889949418422</v>
+        <v>2.364572048799766</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.926973689129509</v>
+        <v>-6.920835614594315</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3011812721353948</v>
+        <v>0.3036365019494727</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.12399639129603</v>
+        <v>-1.191192892327122</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.397929337323329</v>
+        <v>2.357611436704673</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.684825295675651</v>
+        <v>-6.678687221140457</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4125029838980812</v>
+        <v>0.414958213712159</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.12399639129603</v>
+        <v>-1.191192892327122</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.412391691704472</v>
+        <v>2.372073791085816</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.621595923907303</v>
+        <v>-6.615457849372109</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4323268530646156</v>
+        <v>0.434782082878693</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.12399639129603</v>
+        <v>-1.191192892327122</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.406923812163667</v>
+        <v>2.366605911545011</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.435108231530297</v>
+        <v>-6.428970156995103</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5044200240259951</v>
+        <v>0.5068752538400725</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.9375086989190236</v>
+        <v>-1.004705199950116</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.516314521600447</v>
+        <v>2.475996620981792</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.413959032626853</v>
+        <v>-6.407820958091659</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5205806818246979</v>
+        <v>0.5230359116387753</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.9163595000155802</v>
+        <v>-0.9835560010466728</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.536705019179839</v>
+        <v>2.496387118561183</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.170193590643409</v>
+        <v>-6.164055516108215</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6138675669651263</v>
+        <v>0.6163227967792038</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.9163595000155802</v>
+        <v>-0.9835560010466728</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.53248572752689</v>
+        <v>2.492167826908234</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.906165523450149</v>
+        <v>-5.900027448914955</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7216031077624465</v>
+        <v>0.7240583375765239</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.7144941011996266</v>
+        <v>-0.7816906022307193</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.655729280736478</v>
+        <v>2.615411380117822</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.656315129501074</v>
+        <v>-5.65017705496588</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8142853403257786</v>
+        <v>0.816740570139856</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.7144941011996266</v>
+        <v>-0.7816906022307193</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.64847135572018</v>
+        <v>2.608153455101524</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.352747640497095</v>
+        <v>-5.346609565961901</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9393114594480187</v>
+        <v>0.9417666892620962</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.7144941011996266</v>
+        <v>-0.7816906022307193</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.652070479240829</v>
+        <v>2.611752578622173</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.279267731645081</v>
+        <v>-5.273129657109887</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9820309290433782</v>
+        <v>0.9844861588574556</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.6410141923476123</v>
+        <v>-0.7082106933787049</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.709485930606591</v>
+        <v>2.669168029987935</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.054234731976258</v>
+        <v>-5.048096657441064</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.071064606527204</v>
+        <v>1.073519836341282</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.4159811926787894</v>
+        <v>-0.4831776937098821</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.843526208024182</v>
+        <v>2.803208307405526</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.839600354339852</v>
+        <v>-4.833462279804658</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.161613158636084</v>
+        <v>1.164068388450162</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.2013468150423826</v>
+        <v>-0.2685433160734753</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.977001635660343</v>
+        <v>2.936683735041687</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.5729999973655</v>
+        <v>-4.566861922830306</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.24944756020962</v>
+        <v>1.251902790023698</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.2013468150423826</v>
+        <v>-0.2685433160734753</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.958195894444139</v>
+        <v>2.917877993825483</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.332569500560639</v>
+        <v>-4.326431426025446</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.347362835556442</v>
+        <v>1.34981806537052</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.03908368176247767</v>
+        <v>-0.02811281926861497</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.104197269151932</v>
+        <v>3.063879368533276</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.089778692911194</v>
+        <v>-4.083640618376</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.44840847245104</v>
+        <v>1.450863702265118</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.03908368176247767</v>
+        <v>-0.02811281926861497</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.108126582986753</v>
+        <v>3.067808682368097</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234997</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-3.850173601304105</v>
+        <v>-3.844035526768911</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.544929093011216</v>
+        <v>1.547384322825294</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1061316294309722</v>
+        <v>0.03893512839987956</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.149033935505189</v>
+        <v>3.108716034886533</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.500893714587327</v>
+        <v>3.509795375208456</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.080957043693927</v>
+        <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.604563963448825</v>
+        <v>-3.601286459802075</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.63877503400065</v>
+        <v>1.641482020832022</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1061316294309722</v>
+        <v>0.03893512839987956</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.144636021352511</v>
+        <v>3.105714106106527</v>
       </c>
     </row>
   </sheetData>
